--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113680450</v>
       </c>
       <c r="B2" t="n">
-        <v>88716</v>
+        <v>88718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680447</v>
+        <v>113680457</v>
       </c>
       <c r="B3" t="n">
-        <v>91400</v>
+        <v>88718</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613142</v>
+        <v>613180</v>
       </c>
       <c r="R3" t="n">
-        <v>7085935</v>
+        <v>7085940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680457</v>
+        <v>113680447</v>
       </c>
       <c r="B4" t="n">
-        <v>88716</v>
+        <v>91402</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613180</v>
+        <v>613142</v>
       </c>
       <c r="R4" t="n">
-        <v>7085940</v>
+        <v>7085935</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680453</v>
+        <v>113680454</v>
       </c>
       <c r="B5" t="n">
-        <v>91380</v>
+        <v>88718</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613146</v>
+        <v>613148</v>
       </c>
       <c r="R5" t="n">
-        <v>7085818</v>
+        <v>7085851</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680454</v>
+        <v>113680458</v>
       </c>
       <c r="B6" t="n">
-        <v>88716</v>
+        <v>91382</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613148</v>
+        <v>613212</v>
       </c>
       <c r="R6" t="n">
-        <v>7085851</v>
+        <v>7085935</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680455</v>
+        <v>113680448</v>
       </c>
       <c r="B7" t="n">
-        <v>91380</v>
+        <v>91384</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613137</v>
+        <v>613219</v>
       </c>
       <c r="R7" t="n">
-        <v>7085897</v>
+        <v>7085708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
         <v>113680452</v>
       </c>
       <c r="B8" t="n">
-        <v>88716</v>
+        <v>88718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680456</v>
+        <v>113680449</v>
       </c>
       <c r="B9" t="n">
-        <v>91404</v>
+        <v>91389</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2059</v>
+        <v>1435</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613139</v>
+        <v>613233</v>
       </c>
       <c r="R9" t="n">
-        <v>7085897</v>
+        <v>7085706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680449</v>
+        <v>113680451</v>
       </c>
       <c r="B10" t="n">
-        <v>91387</v>
+        <v>88718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1435</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613233</v>
+        <v>613173</v>
       </c>
       <c r="R10" t="n">
-        <v>7085706</v>
+        <v>7085734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1674,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680448</v>
+        <v>113680453</v>
       </c>
       <c r="B11" t="n">
         <v>91382</v>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613219</v>
+        <v>613146</v>
       </c>
       <c r="R11" t="n">
-        <v>7085708</v>
+        <v>7085818</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680458</v>
+        <v>113680455</v>
       </c>
       <c r="B12" t="n">
-        <v>91380</v>
+        <v>91382</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613212</v>
+        <v>613137</v>
       </c>
       <c r="R12" t="n">
-        <v>7085935</v>
+        <v>7085897</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680451</v>
+        <v>113680456</v>
       </c>
       <c r="B13" t="n">
-        <v>88716</v>
+        <v>91406</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613173</v>
+        <v>613139</v>
       </c>
       <c r="R13" t="n">
-        <v>7085734</v>
+        <v>7085897</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680450</v>
+        <v>113680456</v>
       </c>
       <c r="B2" t="n">
-        <v>88718</v>
+        <v>91406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613209</v>
+        <v>613139</v>
       </c>
       <c r="R2" t="n">
-        <v>7085714</v>
+        <v>7085897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680457</v>
+        <v>113680448</v>
       </c>
       <c r="B3" t="n">
-        <v>88718</v>
+        <v>91384</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613180</v>
+        <v>613219</v>
       </c>
       <c r="R3" t="n">
-        <v>7085940</v>
+        <v>7085708</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680447</v>
+        <v>113680449</v>
       </c>
       <c r="B4" t="n">
-        <v>91402</v>
+        <v>91389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>1435</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613142</v>
+        <v>613233</v>
       </c>
       <c r="R4" t="n">
-        <v>7085935</v>
+        <v>7085706</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680454</v>
+        <v>113680451</v>
       </c>
       <c r="B5" t="n">
         <v>88718</v>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613148</v>
+        <v>613173</v>
       </c>
       <c r="R5" t="n">
-        <v>7085851</v>
+        <v>7085734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680458</v>
+        <v>113680455</v>
       </c>
       <c r="B6" t="n">
         <v>91382</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613212</v>
+        <v>613137</v>
       </c>
       <c r="R6" t="n">
-        <v>7085935</v>
+        <v>7085897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680448</v>
+        <v>113680458</v>
       </c>
       <c r="B7" t="n">
-        <v>91384</v>
+        <v>91382</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613219</v>
+        <v>613212</v>
       </c>
       <c r="R7" t="n">
-        <v>7085708</v>
+        <v>7085935</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680452</v>
+        <v>113680454</v>
       </c>
       <c r="B8" t="n">
         <v>88718</v>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613146</v>
+        <v>613148</v>
       </c>
       <c r="R8" t="n">
-        <v>7085807</v>
+        <v>7085851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680449</v>
+        <v>113680447</v>
       </c>
       <c r="B9" t="n">
-        <v>91389</v>
+        <v>91402</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1435</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613233</v>
+        <v>613142</v>
       </c>
       <c r="R9" t="n">
-        <v>7085706</v>
+        <v>7085935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1563,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680451</v>
+        <v>113680452</v>
       </c>
       <c r="B10" t="n">
         <v>88718</v>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613173</v>
+        <v>613146</v>
       </c>
       <c r="R10" t="n">
-        <v>7085734</v>
+        <v>7085807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680453</v>
+        <v>113680450</v>
       </c>
       <c r="B11" t="n">
-        <v>91382</v>
+        <v>88718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613146</v>
+        <v>613209</v>
       </c>
       <c r="R11" t="n">
-        <v>7085818</v>
+        <v>7085714</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680455</v>
+        <v>113680457</v>
       </c>
       <c r="B12" t="n">
-        <v>91382</v>
+        <v>88718</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613137</v>
+        <v>613180</v>
       </c>
       <c r="R12" t="n">
-        <v>7085897</v>
+        <v>7085940</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680456</v>
+        <v>113680453</v>
       </c>
       <c r="B13" t="n">
-        <v>91406</v>
+        <v>91382</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613139</v>
+        <v>613146</v>
       </c>
       <c r="R13" t="n">
-        <v>7085897</v>
+        <v>7085818</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680456</v>
+        <v>113680457</v>
       </c>
       <c r="B2" t="n">
-        <v>91406</v>
+        <v>88722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613139</v>
+        <v>613180</v>
       </c>
       <c r="R2" t="n">
-        <v>7085897</v>
+        <v>7085940</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680448</v>
+        <v>113680451</v>
       </c>
       <c r="B3" t="n">
-        <v>91384</v>
+        <v>88722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613219</v>
+        <v>613173</v>
       </c>
       <c r="R3" t="n">
-        <v>7085708</v>
+        <v>7085734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680449</v>
+        <v>113680448</v>
       </c>
       <c r="B4" t="n">
-        <v>91389</v>
+        <v>91388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1435</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613233</v>
+        <v>613219</v>
       </c>
       <c r="R4" t="n">
-        <v>7085706</v>
+        <v>7085708</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680451</v>
+        <v>113680452</v>
       </c>
       <c r="B5" t="n">
-        <v>88718</v>
+        <v>88722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613173</v>
+        <v>613146</v>
       </c>
       <c r="R5" t="n">
-        <v>7085734</v>
+        <v>7085807</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680455</v>
+        <v>113680450</v>
       </c>
       <c r="B6" t="n">
-        <v>91382</v>
+        <v>88722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613137</v>
+        <v>613209</v>
       </c>
       <c r="R6" t="n">
-        <v>7085897</v>
+        <v>7085714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680458</v>
+        <v>113680456</v>
       </c>
       <c r="B7" t="n">
-        <v>91382</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613212</v>
+        <v>613139</v>
       </c>
       <c r="R7" t="n">
-        <v>7085935</v>
+        <v>7085897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680454</v>
+        <v>113680458</v>
       </c>
       <c r="B8" t="n">
-        <v>88718</v>
+        <v>91386</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613148</v>
+        <v>613212</v>
       </c>
       <c r="R8" t="n">
-        <v>7085851</v>
+        <v>7085935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680447</v>
+        <v>113680454</v>
       </c>
       <c r="B9" t="n">
-        <v>91402</v>
+        <v>88722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613142</v>
+        <v>613148</v>
       </c>
       <c r="R9" t="n">
-        <v>7085935</v>
+        <v>7085851</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680452</v>
+        <v>113680455</v>
       </c>
       <c r="B10" t="n">
-        <v>88718</v>
+        <v>91386</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613146</v>
+        <v>613137</v>
       </c>
       <c r="R10" t="n">
-        <v>7085807</v>
+        <v>7085897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680450</v>
+        <v>113680449</v>
       </c>
       <c r="B11" t="n">
-        <v>88718</v>
+        <v>91393</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>1435</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613209</v>
+        <v>613233</v>
       </c>
       <c r="R11" t="n">
-        <v>7085714</v>
+        <v>7085706</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680457</v>
+        <v>113680447</v>
       </c>
       <c r="B12" t="n">
-        <v>88718</v>
+        <v>91406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613180</v>
+        <v>613142</v>
       </c>
       <c r="R12" t="n">
-        <v>7085940</v>
+        <v>7085935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1899,7 @@
         <v>113680453</v>
       </c>
       <c r="B13" t="n">
-        <v>91382</v>
+        <v>91386</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680457</v>
+        <v>113680451</v>
       </c>
       <c r="B2" t="n">
         <v>88722</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613180</v>
+        <v>613173</v>
       </c>
       <c r="R2" t="n">
-        <v>7085940</v>
+        <v>7085734</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680451</v>
+        <v>113680455</v>
       </c>
       <c r="B3" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613173</v>
+        <v>613137</v>
       </c>
       <c r="R3" t="n">
-        <v>7085734</v>
+        <v>7085897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680452</v>
+        <v>113680449</v>
       </c>
       <c r="B5" t="n">
-        <v>88722</v>
+        <v>91393</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>1435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613146</v>
+        <v>613233</v>
       </c>
       <c r="R5" t="n">
-        <v>7085807</v>
+        <v>7085706</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680450</v>
+        <v>113680447</v>
       </c>
       <c r="B6" t="n">
-        <v>88722</v>
+        <v>91406</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613209</v>
+        <v>613142</v>
       </c>
       <c r="R6" t="n">
-        <v>7085714</v>
+        <v>7085935</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680458</v>
+        <v>113680457</v>
       </c>
       <c r="B8" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613212</v>
+        <v>613180</v>
       </c>
       <c r="R8" t="n">
-        <v>7085935</v>
+        <v>7085940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680454</v>
+        <v>113680452</v>
       </c>
       <c r="B9" t="n">
         <v>88722</v>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613148</v>
+        <v>613146</v>
       </c>
       <c r="R9" t="n">
-        <v>7085851</v>
+        <v>7085807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680455</v>
+        <v>113680450</v>
       </c>
       <c r="B10" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613137</v>
+        <v>613209</v>
       </c>
       <c r="R10" t="n">
-        <v>7085897</v>
+        <v>7085714</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680449</v>
+        <v>113680454</v>
       </c>
       <c r="B11" t="n">
-        <v>91393</v>
+        <v>88722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1690,21 +1690,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1435</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613233</v>
+        <v>613148</v>
       </c>
       <c r="R11" t="n">
-        <v>7085706</v>
+        <v>7085851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680447</v>
+        <v>113680458</v>
       </c>
       <c r="B12" t="n">
-        <v>91406</v>
+        <v>91386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,7 +1825,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613142</v>
+        <v>613212</v>
       </c>
       <c r="R12" t="n">
         <v>7085935</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680451</v>
+        <v>113680454</v>
       </c>
       <c r="B2" t="n">
         <v>88722</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613173</v>
+        <v>613148</v>
       </c>
       <c r="R2" t="n">
-        <v>7085734</v>
+        <v>7085851</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680455</v>
+        <v>113680449</v>
       </c>
       <c r="B3" t="n">
-        <v>91386</v>
+        <v>91393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>1435</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613137</v>
+        <v>613233</v>
       </c>
       <c r="R3" t="n">
-        <v>7085897</v>
+        <v>7085706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680448</v>
+        <v>113680453</v>
       </c>
       <c r="B4" t="n">
-        <v>91388</v>
+        <v>91386</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613219</v>
+        <v>613146</v>
       </c>
       <c r="R4" t="n">
-        <v>7085708</v>
+        <v>7085818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680449</v>
+        <v>113680451</v>
       </c>
       <c r="B5" t="n">
-        <v>91393</v>
+        <v>88722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1435</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613233</v>
+        <v>613173</v>
       </c>
       <c r="R5" t="n">
-        <v>7085706</v>
+        <v>7085734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680447</v>
+        <v>113680456</v>
       </c>
       <c r="B6" t="n">
-        <v>91406</v>
+        <v>91410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613142</v>
+        <v>613139</v>
       </c>
       <c r="R6" t="n">
-        <v>7085935</v>
+        <v>7085897</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680456</v>
+        <v>113680452</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>88722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613139</v>
+        <v>613146</v>
       </c>
       <c r="R7" t="n">
-        <v>7085897</v>
+        <v>7085807</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680452</v>
+        <v>113680455</v>
       </c>
       <c r="B9" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613146</v>
+        <v>613137</v>
       </c>
       <c r="R9" t="n">
-        <v>7085807</v>
+        <v>7085897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680450</v>
+        <v>113680447</v>
       </c>
       <c r="B10" t="n">
-        <v>88722</v>
+        <v>91406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613209</v>
+        <v>613142</v>
       </c>
       <c r="R10" t="n">
-        <v>7085714</v>
+        <v>7085935</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680454</v>
+        <v>113680458</v>
       </c>
       <c r="B11" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613148</v>
+        <v>613212</v>
       </c>
       <c r="R11" t="n">
-        <v>7085851</v>
+        <v>7085935</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680458</v>
+        <v>113680450</v>
       </c>
       <c r="B12" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613212</v>
+        <v>613209</v>
       </c>
       <c r="R12" t="n">
-        <v>7085935</v>
+        <v>7085714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680453</v>
+        <v>113680448</v>
       </c>
       <c r="B13" t="n">
-        <v>91386</v>
+        <v>91388</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1912,21 +1912,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613146</v>
+        <v>613219</v>
       </c>
       <c r="R13" t="n">
-        <v>7085818</v>
+        <v>7085708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680454</v>
+        <v>113680455</v>
       </c>
       <c r="B2" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613148</v>
+        <v>613137</v>
       </c>
       <c r="R2" t="n">
-        <v>7085851</v>
+        <v>7085897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680449</v>
+        <v>113680457</v>
       </c>
       <c r="B3" t="n">
-        <v>91393</v>
+        <v>88722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1435</v>
+        <v>6276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613233</v>
+        <v>613180</v>
       </c>
       <c r="R3" t="n">
-        <v>7085706</v>
+        <v>7085940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680453</v>
+        <v>113680451</v>
       </c>
       <c r="B4" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613146</v>
+        <v>613173</v>
       </c>
       <c r="R4" t="n">
-        <v>7085818</v>
+        <v>7085734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680451</v>
+        <v>113680456</v>
       </c>
       <c r="B5" t="n">
-        <v>88722</v>
+        <v>91410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1020,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613173</v>
+        <v>613139</v>
       </c>
       <c r="R5" t="n">
-        <v>7085734</v>
+        <v>7085897</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680456</v>
+        <v>113680450</v>
       </c>
       <c r="B6" t="n">
-        <v>91410</v>
+        <v>88722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,25 +1131,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613139</v>
+        <v>613209</v>
       </c>
       <c r="R6" t="n">
-        <v>7085897</v>
+        <v>7085714</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680452</v>
+        <v>113680453</v>
       </c>
       <c r="B7" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
         <v>613146</v>
       </c>
       <c r="R7" t="n">
-        <v>7085807</v>
+        <v>7085818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680457</v>
+        <v>113680458</v>
       </c>
       <c r="B8" t="n">
-        <v>88722</v>
+        <v>91386</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613180</v>
+        <v>613212</v>
       </c>
       <c r="R8" t="n">
-        <v>7085940</v>
+        <v>7085935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680455</v>
+        <v>113680449</v>
       </c>
       <c r="B9" t="n">
-        <v>91386</v>
+        <v>91393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>1435</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613137</v>
+        <v>613233</v>
       </c>
       <c r="R9" t="n">
-        <v>7085897</v>
+        <v>7085706</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680447</v>
+        <v>113680448</v>
       </c>
       <c r="B10" t="n">
-        <v>91406</v>
+        <v>91388</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,25 +1575,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613142</v>
+        <v>613219</v>
       </c>
       <c r="R10" t="n">
-        <v>7085935</v>
+        <v>7085708</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680458</v>
+        <v>113680454</v>
       </c>
       <c r="B11" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613212</v>
+        <v>613148</v>
       </c>
       <c r="R11" t="n">
-        <v>7085935</v>
+        <v>7085851</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680450</v>
+        <v>113680447</v>
       </c>
       <c r="B12" t="n">
-        <v>88722</v>
+        <v>91406</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613209</v>
+        <v>613142</v>
       </c>
       <c r="R12" t="n">
-        <v>7085714</v>
+        <v>7085935</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680448</v>
+        <v>113680452</v>
       </c>
       <c r="B13" t="n">
-        <v>91388</v>
+        <v>88722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1908,25 +1908,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613219</v>
+        <v>613146</v>
       </c>
       <c r="R13" t="n">
-        <v>7085708</v>
+        <v>7085807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680455</v>
+        <v>113680450</v>
       </c>
       <c r="B2" t="n">
-        <v>91386</v>
+        <v>88722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613137</v>
+        <v>613209</v>
       </c>
       <c r="R2" t="n">
-        <v>7085897</v>
+        <v>7085714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680457</v>
+        <v>113680451</v>
       </c>
       <c r="B3" t="n">
         <v>88722</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613180</v>
+        <v>613173</v>
       </c>
       <c r="R3" t="n">
-        <v>7085940</v>
+        <v>7085734</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680451</v>
+        <v>113680457</v>
       </c>
       <c r="B4" t="n">
         <v>88722</v>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613173</v>
+        <v>613180</v>
       </c>
       <c r="R4" t="n">
-        <v>7085734</v>
+        <v>7085940</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680456</v>
+        <v>113680455</v>
       </c>
       <c r="B5" t="n">
-        <v>91410</v>
+        <v>91386</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613139</v>
+        <v>613137</v>
       </c>
       <c r="R5" t="n">
         <v>7085897</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680450</v>
+        <v>113680454</v>
       </c>
       <c r="B6" t="n">
         <v>88722</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613209</v>
+        <v>613148</v>
       </c>
       <c r="R6" t="n">
-        <v>7085714</v>
+        <v>7085851</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680453</v>
+        <v>113680449</v>
       </c>
       <c r="B7" t="n">
-        <v>91386</v>
+        <v>91393</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613146</v>
+        <v>613233</v>
       </c>
       <c r="R7" t="n">
-        <v>7085818</v>
+        <v>7085706</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113680449</v>
+        <v>113680447</v>
       </c>
       <c r="B9" t="n">
-        <v>91393</v>
+        <v>91406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1435</v>
+        <v>4366</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613233</v>
+        <v>613142</v>
       </c>
       <c r="R9" t="n">
-        <v>7085706</v>
+        <v>7085935</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680448</v>
+        <v>113680456</v>
       </c>
       <c r="B10" t="n">
-        <v>91388</v>
+        <v>91410</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1579,21 +1579,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613219</v>
+        <v>613139</v>
       </c>
       <c r="R10" t="n">
-        <v>7085708</v>
+        <v>7085897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680454</v>
+        <v>113680448</v>
       </c>
       <c r="B11" t="n">
-        <v>88722</v>
+        <v>91388</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1686,25 +1686,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613148</v>
+        <v>613219</v>
       </c>
       <c r="R11" t="n">
-        <v>7085851</v>
+        <v>7085708</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,10 +1785,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680447</v>
+        <v>113680453</v>
       </c>
       <c r="B12" t="n">
-        <v>91406</v>
+        <v>91386</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613142</v>
+        <v>613146</v>
       </c>
       <c r="R12" t="n">
-        <v>7085935</v>
+        <v>7085818</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113680448</v>
+        <v>113680449</v>
       </c>
       <c r="B2" t="n">
-        <v>93198</v>
+        <v>93270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613219</v>
+        <v>613233</v>
       </c>
       <c r="R2" t="n">
-        <v>7085708</v>
+        <v>7085706</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113680447</v>
+        <v>113680456</v>
       </c>
       <c r="B3" t="n">
-        <v>93216</v>
+        <v>93287</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613142</v>
+        <v>613139</v>
       </c>
       <c r="R3" t="n">
-        <v>7085935</v>
+        <v>7085897</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113680451</v>
+        <v>113680453</v>
       </c>
       <c r="B4" t="n">
-        <v>90698</v>
+        <v>93263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613172</v>
+        <v>613146</v>
       </c>
       <c r="R4" t="n">
-        <v>7085734</v>
+        <v>7085818</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113680453</v>
+        <v>113680455</v>
       </c>
       <c r="B5" t="n">
-        <v>93196</v>
+        <v>93263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613146</v>
+        <v>613137</v>
       </c>
       <c r="R5" t="n">
-        <v>7085818</v>
+        <v>7085898</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,32 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113680452</v>
+        <v>113680458</v>
       </c>
       <c r="B6" t="n">
-        <v>90698</v>
+        <v>93263</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613146</v>
+        <v>613212</v>
       </c>
       <c r="R6" t="n">
-        <v>7085807</v>
+        <v>7085934</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113680455</v>
+        <v>113680448</v>
       </c>
       <c r="B7" t="n">
-        <v>93196</v>
+        <v>93265</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613137</v>
+        <v>613219</v>
       </c>
       <c r="R7" t="n">
-        <v>7085898</v>
+        <v>7085708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113680456</v>
+        <v>113680447</v>
       </c>
       <c r="B8" t="n">
-        <v>93220</v>
+        <v>93283</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613139</v>
+        <v>613142</v>
       </c>
       <c r="R8" t="n">
-        <v>7085897</v>
+        <v>7085935</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,7 +1420,7 @@
         <v>113680450</v>
       </c>
       <c r="B9" t="n">
-        <v>90698</v>
+        <v>90756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113680457</v>
+        <v>113680451</v>
       </c>
       <c r="B10" t="n">
-        <v>90698</v>
+        <v>90756</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1558,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613180</v>
+        <v>613172</v>
       </c>
       <c r="R10" t="n">
-        <v>7085940</v>
+        <v>7085734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113680454</v>
+        <v>113680452</v>
       </c>
       <c r="B11" t="n">
-        <v>90698</v>
+        <v>90756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613149</v>
+        <v>613146</v>
       </c>
       <c r="R11" t="n">
-        <v>7085851</v>
+        <v>7085807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,32 +1735,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113680458</v>
+        <v>113680454</v>
       </c>
       <c r="B12" t="n">
-        <v>93196</v>
+        <v>90756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613212</v>
+        <v>613149</v>
       </c>
       <c r="R12" t="n">
-        <v>7085934</v>
+        <v>7085851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113680449</v>
+        <v>113680457</v>
       </c>
       <c r="B13" t="n">
-        <v>93203</v>
+        <v>90756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1435</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613233</v>
+        <v>613180</v>
       </c>
       <c r="R13" t="n">
-        <v>7085706</v>
+        <v>7085940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 16087-2022 artfynd.xlsx
+++ b/artfynd/A 16087-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680449</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680453</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680458</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680448</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680447</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680450</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680451</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680454</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,8 +2004,27 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113680457</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>